--- a/assets/SDGym Monthly Run.xlsx
+++ b/assets/SDGym Monthly Run.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,51 +523,35 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -619,71 +603,51 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B4" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -791,156 +755,6 @@
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(1)</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(2)</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -41246,7 +41060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41324,7 +41138,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -41416,7 +41230,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
@@ -41508,7 +41322,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -41612,31 +41426,31 @@
         <v>3.907448</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.101878</v>
+        <v>0.089077</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>19.136963</v>
+        <v>18.854596</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>2.152501</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.041737</v>
+        <v>0.037661</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>1.645835</v>
+        <v>1.665692</v>
       </c>
       <c r="I8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.4331113667912469</v>
+        <v>0.4329123247860583</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.245493</v>
+        <v>0.215815</v>
       </c>
       <c r="L8" s="0" t="n">
-        <v>0.4331113667912469</v>
+        <v>0.4329123247860583</v>
       </c>
       <c r="M8" s="0" t="inlineStr"/>
       <c r="N8" s="0" t="n">
@@ -41646,43 +41460,43 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(1)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>alarm</t>
         </is>
       </c>
       <c r="C9" s="0" t="n">
-        <v>3.907448</v>
+        <v>4.520128</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.089077</v>
+        <v>803.635183</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>18.854596</v>
+        <v>55.864993</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>2.152501</v>
+        <v>7.689256</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.037661</v>
+        <v>1.304962</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>1.665692</v>
+        <v>7.171872</v>
       </c>
       <c r="I9" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.4329123247860583</v>
+        <v>0.9218652777777776</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.215815</v>
+        <v>805.031521</v>
       </c>
       <c r="L9" s="0" t="n">
-        <v>0.4329123247860583</v>
+        <v>0.9218652777777776</v>
       </c>
       <c r="M9" s="0" t="inlineStr"/>
       <c r="N9" s="0" t="n">
@@ -41692,43 +41506,43 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(2)</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>alarm</t>
         </is>
       </c>
       <c r="C10" s="0" t="n">
-        <v>3.907448</v>
+        <v>4.520128</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.091376</v>
+        <v>5.69417</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>18.857236</v>
+        <v>30.007335</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>2.152501</v>
+        <v>4.423055</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.041355</v>
+        <v>0.286296</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>1.67121</v>
+        <v>7.013701999999999</v>
       </c>
       <c r="I10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.43192369766648</v>
+        <v>0.9784544294294296</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.224107</v>
+        <v>6.082344</v>
       </c>
       <c r="L10" s="0" t="n">
-        <v>0.43192369766648</v>
+        <v>0.9784544294294296</v>
       </c>
       <c r="M10" s="0" t="inlineStr"/>
       <c r="N10" s="0" t="n">
@@ -41738,43 +41552,43 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(3)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>alarm</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
-        <v>3.907448</v>
+        <v>4.520128</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.09832200000000001</v>
+        <v>879.166658</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>18.989238</v>
+        <v>60.398094</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>2.152501</v>
+        <v>7.690565</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.039105</v>
+        <v>1.497748</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>1.579989</v>
+        <v>7.034246</v>
       </c>
       <c r="I11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.4340007147880677</v>
+        <v>0.9253466216216216</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.235749</v>
+        <v>880.753483</v>
       </c>
       <c r="L11" s="0" t="n">
-        <v>0.4340007147880677</v>
+        <v>0.9253466216216216</v>
       </c>
       <c r="M11" s="0" t="inlineStr"/>
       <c r="N11" s="0" t="n">
@@ -41784,7 +41598,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
@@ -41796,31 +41610,31 @@
         <v>4.520128</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>803.635183</v>
+        <v>28.088987</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>55.864993</v>
+        <v>61.445582</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>7.689256</v>
+        <v>0.5092680000000001</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>1.304962</v>
+        <v>1.71876</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>7.171872</v>
+        <v>7.003368</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.9218652777777776</v>
+        <v>0.9823706831831832</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>805.031521</v>
+        <v>29.909625</v>
       </c>
       <c r="L12" s="0" t="n">
-        <v>0.9218652777777776</v>
+        <v>0.9823706831831832</v>
       </c>
       <c r="M12" s="0" t="inlineStr"/>
       <c r="N12" s="0" t="n">
@@ -41830,7 +41644,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>ColumnSynthesizer</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -41842,31 +41656,31 @@
         <v>4.520128</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>5.69417</v>
+        <v>8869.99388</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>30.007335</v>
+        <v>739.552157</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>4.423055</v>
+        <v>179.965374</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.286296</v>
+        <v>285.437394</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>7.013701999999999</v>
+        <v>8.781935000000001</v>
       </c>
       <c r="I13" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.9784544294294296</v>
+        <v>0.650246509009009</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>6.082344</v>
+        <v>9155.529596</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>0.9784544294294296</v>
+        <v>0.650246509009009</v>
       </c>
       <c r="M13" s="0" t="inlineStr"/>
       <c r="N13" s="0" t="n">
@@ -41876,7 +41690,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
@@ -41888,31 +41702,31 @@
         <v>4.520128</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>879.166658</v>
+        <v>243.370399</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>60.398094</v>
+        <v>55.883388</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>7.690565</v>
+        <v>1.162265</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>1.497748</v>
+        <v>1.050065</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>7.034246</v>
+        <v>6.993649</v>
       </c>
       <c r="I14" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.9253466216216216</v>
+        <v>0.9727005255255256</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>880.753483</v>
+        <v>244.522342</v>
       </c>
       <c r="L14" s="0" t="n">
-        <v>0.9253466216216216</v>
+        <v>0.9727005255255256</v>
       </c>
       <c r="M14" s="0" t="inlineStr"/>
       <c r="N14" s="0" t="n">
@@ -41922,7 +41736,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>GaussianCopulaSynthesizer</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -41934,31 +41748,31 @@
         <v>4.520128</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>28.088987</v>
+        <v>0.238727</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>61.445582</v>
+        <v>23.047347</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5092680000000001</v>
+        <v>1.284369</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>1.71876</v>
+        <v>0.065604</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>7.003368</v>
+        <v>7.154329</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.9823706831831832</v>
+        <v>0.5019957957957958</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>29.909625</v>
+        <v>0.393408</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>0.9823706831831832</v>
+        <v>0.5019957957957958</v>
       </c>
       <c r="M15" s="0" t="inlineStr"/>
       <c r="N15" s="0" t="n">
@@ -41968,181 +41782,181 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>census</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
-        <v>4.520128</v>
+        <v>98.16560800000001</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>8869.99388</v>
+        <v>34876.798855</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>739.552157</v>
+        <v>3571.097893</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>179.965374</v>
+        <v>73.79253199999999</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>285.437394</v>
+        <v>25.646781</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>8.781935000000001</v>
+        <v>40.796828</v>
       </c>
       <c r="I16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.650246509009009</v>
+        <v>0.8936026852859773</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>9155.529596</v>
+        <v>34902.537012</v>
       </c>
       <c r="L16" s="0" t="n">
-        <v>0.650246509009009</v>
+        <v>0.8936026852859773</v>
       </c>
       <c r="M16" s="0" t="inlineStr"/>
       <c r="N16" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>TVAESynthesizer</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>census</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>4.520128</v>
+        <v>98.16560800000001</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>243.370399</v>
+        <v>19.205512</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>55.883388</v>
+        <v>469.537489</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>1.162265</v>
+        <v>62.32306</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>1.050065</v>
+        <v>0.936343</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>6.993649</v>
+        <v>38.382069</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>1</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.9727005255255256</v>
+        <v>0.8908572860941755</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>244.522342</v>
+        <v>20.243733</v>
       </c>
       <c r="L17" s="0" t="n">
-        <v>0.9727005255255256</v>
+        <v>0.8908572860941755</v>
       </c>
       <c r="M17" s="0" t="inlineStr"/>
       <c r="N17" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>census</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>4.520128</v>
+        <v>98.16560800000001</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.204026</v>
+        <v>35138.974558</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>23.056578</v>
+        <v>3619.118378</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>1.284369</v>
+        <v>73.897561</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.064091</v>
+        <v>32.749124</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>7.035345</v>
+        <v>42.615685</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.5017387012012013</v>
+        <v>0.8903456872967631</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.369995</v>
+        <v>35171.812759</v>
       </c>
       <c r="L18" s="0" t="n">
-        <v>0.5017387012012013</v>
+        <v>0.8903456872967631</v>
       </c>
       <c r="M18" s="0" t="inlineStr"/>
       <c r="N18" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(1)</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>census</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
-        <v>4.520128</v>
+        <v>98.16560800000001</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.238727</v>
+        <v>312.914467</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>23.047347</v>
+        <v>1009.322363</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>1.284369</v>
+        <v>0.593503</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.065604</v>
+        <v>23.233002</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>7.154329</v>
+        <v>37.76455600000001</v>
       </c>
       <c r="I19" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.5019957957957958</v>
+        <v>0.8838066476531389</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.393408</v>
+        <v>336.249347</v>
       </c>
       <c r="L19" s="0" t="n">
-        <v>0.5019957957957958</v>
+        <v>0.8838066476531389</v>
       </c>
       <c r="M19" s="0" t="inlineStr"/>
       <c r="N19" s="0" t="n">
@@ -42152,99 +41966,99 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(2)</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>census</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>4.520128</v>
+        <v>98.16560800000001</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.198898</v>
+        <v>248825.803291</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>23.04663</v>
+        <v>7515.967845</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>1.284369</v>
+        <v>181.749781</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.070816</v>
+        <v>7639.94631</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>7.408401</v>
+        <v>89.417635</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>1</v>
+        <v>0.9999992257970928</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.5011492117117117</v>
+        <v>0.9673627160542336</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.3610899999999999</v>
+        <v>256465.847923</v>
       </c>
       <c r="L20" s="0" t="n">
-        <v>0.5011492117117117</v>
+        <v>0.9673627160542336</v>
       </c>
       <c r="M20" s="0" t="inlineStr"/>
       <c r="N20" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(3)</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>alarm</t>
+          <t>census</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
-        <v>4.520128</v>
+        <v>98.16560800000001</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.206251</v>
+        <v>8946.841756</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>23.058271</v>
+        <v>3571.096198</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>1.284369</v>
+        <v>5.653928</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.061945</v>
+        <v>14.262989</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>7.039246</v>
+        <v>38.374688</v>
       </c>
       <c r="I21" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.5027949324324323</v>
+        <v>0.9182483946141582</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.366518</v>
+        <v>8961.206623</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>0.5027949324324323</v>
+        <v>0.9182483946141582</v>
       </c>
       <c r="M21" s="0" t="inlineStr"/>
       <c r="N21" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -42256,169 +42070,169 @@
         <v>98.16560800000001</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>34876.798855</v>
+        <v>1.112763</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>3571.097893</v>
+        <v>469.460659</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>73.79253199999999</v>
+        <v>62.31429</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>25.646781</v>
+        <v>0.855016</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>40.796828</v>
+        <v>42.282759</v>
       </c>
       <c r="I22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.8936026852859773</v>
+        <v>0.3420143277300588</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>34902.537012</v>
+        <v>2.056856</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>0.8936026852859773</v>
+        <v>0.3420143277300588</v>
       </c>
       <c r="M22" s="0" t="inlineStr"/>
       <c r="N22" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>ColumnSynthesizer</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>19.205512</v>
+        <v>594.926034</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>469.537489</v>
+        <v>32.675612</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>62.32306</v>
+        <v>4.45029</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>0.936343</v>
+        <v>0.667455</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>38.382069</v>
+        <v>2.49356</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>0.7735849056603774</v>
+        <v>1</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>0.8908572860941755</v>
+        <v>0.9229373519173628</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>20.243733</v>
+        <v>595.6848649999999</v>
       </c>
       <c r="L23" s="0" t="n">
-        <v>0.8908572860941755</v>
+        <v>0.9229373519173628</v>
       </c>
       <c r="M23" s="0" t="inlineStr"/>
       <c r="N23" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>35138.974558</v>
+        <v>0.139234</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>3619.118378</v>
+        <v>16.581276</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>73.897561</v>
+        <v>0.861281</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>32.749124</v>
+        <v>0.036634</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>42.615685</v>
+        <v>2.452327</v>
       </c>
       <c r="I24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>0.8903456872967631</v>
+        <v>0.9620961076629098</v>
       </c>
       <c r="K24" s="0" t="n">
-        <v>35171.812759</v>
+        <v>0.277746</v>
       </c>
       <c r="L24" s="0" t="n">
-        <v>0.8903456872967631</v>
+        <v>0.9620961076629098</v>
       </c>
       <c r="M24" s="0" t="inlineStr"/>
       <c r="N24" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>GaussianCopulaSynthesizer</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C25" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>312.914467</v>
+        <v>693.874815</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>1009.322363</v>
+        <v>35.88692</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>0.593503</v>
+        <v>4.451132</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>23.233002</v>
+        <v>0.81546</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>37.76455600000001</v>
+        <v>2.667435</v>
       </c>
       <c r="I25" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>0.8838066476531389</v>
+        <v>0.9025278789579676</v>
       </c>
       <c r="K25" s="0" t="n">
-        <v>336.249347</v>
+        <v>694.779352</v>
       </c>
       <c r="L25" s="0" t="n">
-        <v>0.8838066476531389</v>
+        <v>0.9025278789579676</v>
       </c>
       <c r="M25" s="0" t="inlineStr"/>
       <c r="N25" s="0" t="n">
@@ -42428,135 +42242,135 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C26" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>248825.803291</v>
+        <v>14.080046</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>7515.967845</v>
+        <v>33.341056</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>181.749781</v>
+        <v>0.308887</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>7639.94631</v>
+        <v>0.847302</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>89.417635</v>
+        <v>2.465829</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0.9999992257970928</v>
+        <v>1</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>0.9673627160542336</v>
+        <v>0.9672384890746114</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>256465.847923</v>
+        <v>15.029226</v>
       </c>
       <c r="L26" s="0" t="n">
-        <v>0.9673627160542336</v>
+        <v>0.9672384890746114</v>
       </c>
       <c r="M26" s="0" t="inlineStr"/>
       <c r="N26" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>TVAESynthesizer</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C27" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>8946.841756</v>
+        <v>6200.863679</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>3571.096198</v>
+        <v>728.9940309999999</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>5.653928</v>
+        <v>179.823617</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>14.262989</v>
+        <v>150.061661</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>38.374688</v>
+        <v>3.015543</v>
       </c>
       <c r="I27" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>0.9182483946141582</v>
+        <v>0.9608767019102408</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>8961.206623</v>
+        <v>6351.023662</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>0.9182483946141582</v>
+        <v>0.9608767019102408</v>
       </c>
       <c r="M27" s="0" t="inlineStr"/>
       <c r="N27" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C28" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>1.105292</v>
+        <v>231.129302</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>469.469794</v>
+        <v>32.655389</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>62.31429</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>0.890161</v>
+        <v>0.494794</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>37.621236</v>
+        <v>2.47099</v>
       </c>
       <c r="I28" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>0.3418969402682245</v>
+        <v>0.9569586410553236</v>
       </c>
       <c r="K28" s="0" t="n">
-        <v>2.097331</v>
+        <v>231.725974</v>
       </c>
       <c r="L28" s="0" t="n">
-        <v>0.3418969402682245</v>
+        <v>0.9569586410553236</v>
       </c>
       <c r="M28" s="0" t="inlineStr"/>
       <c r="N28" s="0" t="n">
@@ -42566,43 +42380,43 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(1)</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C29" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>3.200128</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>1.112763</v>
+        <v>0.158564</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>469.460659</v>
+        <v>16.579971</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>62.31429</v>
+        <v>0.861279</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0.855016</v>
+        <v>0.044558</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>42.282759</v>
+        <v>2.678099</v>
       </c>
       <c r="I29" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>0.3420143277300588</v>
+        <v>0.6799587875893454</v>
       </c>
       <c r="K29" s="0" t="n">
-        <v>2.056856</v>
+        <v>0.292199</v>
       </c>
       <c r="L29" s="0" t="n">
-        <v>0.3420143277300588</v>
+        <v>0.6799587875893454</v>
       </c>
       <c r="M29" s="0" t="inlineStr"/>
       <c r="N29" s="0" t="n">
@@ -42612,181 +42426,181 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(2)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>covtype</t>
         </is>
       </c>
       <c r="C30" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>255.645408</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>1.036543</v>
+        <v>40248.181123</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>469.461221</v>
+        <v>3483.221779</v>
       </c>
       <c r="F30" s="0" t="n">
-        <v>62.31429</v>
+        <v>7.503442</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>0.836355</v>
+        <v>46.234079</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>40.449821</v>
+        <v>78.58078099999999</v>
       </c>
       <c r="I30" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>0.3419759745039388</v>
+        <v>0.9396237508326822</v>
       </c>
       <c r="K30" s="0" t="n">
-        <v>1.964274</v>
+        <v>40294.506578</v>
       </c>
       <c r="L30" s="0" t="n">
-        <v>0.3419759745039388</v>
+        <v>0.9396237508326822</v>
       </c>
       <c r="M30" s="0" t="inlineStr"/>
       <c r="N30" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(3)</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>census</t>
+          <t>covtype</t>
         </is>
       </c>
       <c r="C31" s="0" t="n">
-        <v>98.16560800000001</v>
+        <v>255.645408</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>1.100477</v>
+        <v>62.498895</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>469.479278</v>
+        <v>1287.931214</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>62.31429</v>
+        <v>255.674697</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>0.833324</v>
+        <v>1.900782</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>41.169019</v>
+        <v>3515.466492</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>1</v>
+        <v>0.492734244888073</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>0.341881471376205</v>
+        <v>0.7135732076047883</v>
       </c>
       <c r="K31" s="0" t="n">
-        <v>2.032123</v>
+        <v>64.501555</v>
       </c>
       <c r="L31" s="0" t="n">
-        <v>0.341881471376205</v>
+        <v>0.7135732076047883</v>
       </c>
       <c r="M31" s="0" t="inlineStr"/>
       <c r="N31" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>covtype</t>
         </is>
       </c>
       <c r="C32" s="0" t="n">
-        <v>3.200128</v>
+        <v>255.645408</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>594.926034</v>
+        <v>44676.97402</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>32.675612</v>
+        <v>3739.373886</v>
       </c>
       <c r="F32" s="0" t="n">
-        <v>4.45029</v>
+        <v>8.101912</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>0.667455</v>
+        <v>124.116482</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>2.49356</v>
+        <v>61.226681</v>
       </c>
       <c r="I32" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>0.9229373519173628</v>
+        <v>0.674561704813339</v>
       </c>
       <c r="K32" s="0" t="n">
-        <v>595.6848649999999</v>
+        <v>44801.179579</v>
       </c>
       <c r="L32" s="0" t="n">
-        <v>0.9229373519173628</v>
+        <v>0.674561704813339</v>
       </c>
       <c r="M32" s="0" t="inlineStr"/>
       <c r="N32" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>ColumnSynthesizer</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>covtype</t>
         </is>
       </c>
       <c r="C33" s="0" t="n">
-        <v>3.200128</v>
+        <v>255.645408</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.139234</v>
+        <v>377.064984</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>16.581276</v>
+        <v>2625.842367</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>0.861281</v>
+        <v>0.730716</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>0.036634</v>
+        <v>71.379243</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>2.452327</v>
+        <v>60.59037</v>
       </c>
       <c r="I33" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>0.9620961076629098</v>
+        <v>0.5949887839771277</v>
       </c>
       <c r="K33" s="0" t="n">
-        <v>0.277746</v>
+        <v>448.546105</v>
       </c>
       <c r="L33" s="0" t="n">
-        <v>0.9620961076629098</v>
+        <v>0.5949887839771277</v>
       </c>
       <c r="M33" s="0" t="inlineStr"/>
       <c r="N33" s="0" t="n">
@@ -42796,45 +42610,33 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="n">
-        <v>3.200128</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>693.874815</v>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>35.88692</v>
-      </c>
-      <c r="F34" s="0" t="n">
-        <v>4.451132</v>
-      </c>
-      <c r="G34" s="0" t="n">
-        <v>0.81546</v>
-      </c>
-      <c r="H34" s="0" t="n">
-        <v>2.667435</v>
-      </c>
-      <c r="I34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="0" t="n">
-        <v>0.9025278789579676</v>
-      </c>
+          <t>covtype</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr"/>
+      <c r="D34" s="0" t="inlineStr"/>
+      <c r="E34" s="0" t="inlineStr"/>
+      <c r="F34" s="0" t="inlineStr"/>
+      <c r="G34" s="0" t="inlineStr"/>
+      <c r="H34" s="0" t="inlineStr"/>
+      <c r="I34" s="0" t="inlineStr"/>
+      <c r="J34" s="0" t="inlineStr"/>
       <c r="K34" s="0" t="n">
-        <v>694.779352</v>
+        <v>345600.137427</v>
       </c>
       <c r="L34" s="0" t="n">
-        <v>0.9025278789579676</v>
-      </c>
-      <c r="M34" s="0" t="inlineStr"/>
+        <v>0.4340007147880677</v>
+      </c>
+      <c r="M34" s="0" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
       <c r="N34" s="0" t="n">
         <v>0</v>
       </c>
@@ -42842,135 +42644,135 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>GaussianCopulaSynthesizer</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>covtype</t>
         </is>
       </c>
       <c r="C35" s="0" t="n">
-        <v>3.200128</v>
+        <v>255.645408</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>14.080046</v>
+        <v>21309.350192</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>33.341056</v>
+        <v>3483.232857</v>
       </c>
       <c r="F35" s="0" t="n">
-        <v>0.308887</v>
+        <v>10.32129</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>0.847302</v>
+        <v>32.411723</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>2.465829</v>
+        <v>74.74739600000001</v>
       </c>
       <c r="I35" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>0.9672384890746114</v>
+        <v>0.9573278212792348</v>
       </c>
       <c r="K35" s="0" t="n">
-        <v>15.029226</v>
+        <v>21341.863793</v>
       </c>
       <c r="L35" s="0" t="n">
-        <v>0.9672384890746114</v>
+        <v>0.9573278212792348</v>
       </c>
       <c r="M35" s="0" t="inlineStr"/>
       <c r="N35" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>covtype</t>
         </is>
       </c>
       <c r="C36" s="0" t="n">
-        <v>3.200128</v>
+        <v>255.645408</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>6200.863679</v>
+        <v>0.967338</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>728.9940309999999</v>
+        <v>1287.762884</v>
       </c>
       <c r="F36" s="0" t="n">
-        <v>179.823617</v>
+        <v>255.648398</v>
       </c>
       <c r="G36" s="0" t="n">
-        <v>150.061661</v>
+        <v>0.547588</v>
       </c>
       <c r="H36" s="0" t="n">
-        <v>3.015543</v>
+        <v>91.68889900000001</v>
       </c>
       <c r="I36" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>0.9608767019102408</v>
+        <v>0.7521850232083631</v>
       </c>
       <c r="K36" s="0" t="n">
-        <v>6351.023662</v>
+        <v>1.604003</v>
       </c>
       <c r="L36" s="0" t="n">
-        <v>0.9608767019102408</v>
+        <v>0.7521850232083631</v>
       </c>
       <c r="M36" s="0" t="inlineStr"/>
       <c r="N36" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>TVAESynthesizer</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C37" s="0" t="n">
-        <v>3.200128</v>
+        <v>0.200128</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>231.129302</v>
+        <v>72.156249</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>32.655389</v>
+        <v>16.143328</v>
       </c>
       <c r="F37" s="0" t="n">
-        <v>0.8604000000000001</v>
+        <v>5.425123</v>
       </c>
       <c r="G37" s="0" t="n">
-        <v>0.494794</v>
+        <v>1.182253</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>2.47099</v>
+        <v>1.252887</v>
       </c>
       <c r="I37" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>0.9569586410553236</v>
+        <v>0.6957054551909917</v>
       </c>
       <c r="K37" s="0" t="n">
-        <v>231.725974</v>
+        <v>73.429878</v>
       </c>
       <c r="L37" s="0" t="n">
-        <v>0.9569586410553236</v>
+        <v>0.6957054551909917</v>
       </c>
       <c r="M37" s="0" t="inlineStr"/>
       <c r="N37" s="0" t="n">
@@ -42980,43 +42782,43 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C38" s="0" t="n">
-        <v>3.200128</v>
+        <v>0.200128</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>0.123347</v>
+        <v>0.54053</v>
       </c>
       <c r="E38" s="0" t="n">
-        <v>16.584536</v>
+        <v>1.181518</v>
       </c>
       <c r="F38" s="0" t="n">
-        <v>0.861279</v>
+        <v>0.24771</v>
       </c>
       <c r="G38" s="0" t="n">
-        <v>0.042186</v>
+        <v>0.042428</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>2.495924</v>
+        <v>1.834723</v>
       </c>
       <c r="I38" s="0" t="n">
-        <v>1</v>
+        <v>0.2796155555555556</v>
       </c>
       <c r="J38" s="0" t="n">
-        <v>0.6797352366156708</v>
+        <v>0.2518450866737775</v>
       </c>
       <c r="K38" s="0" t="n">
-        <v>0.267411</v>
+        <v>0.684836</v>
       </c>
       <c r="L38" s="0" t="n">
-        <v>0.6797352366156708</v>
+        <v>0.2518450866737775</v>
       </c>
       <c r="M38" s="0" t="inlineStr"/>
       <c r="N38" s="0" t="n">
@@ -43026,43 +42828,43 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(1)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C39" s="0" t="n">
-        <v>3.200128</v>
+        <v>0.200128</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>0.158564</v>
+        <v>77.71141</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>16.579971</v>
+        <v>16.514218</v>
       </c>
       <c r="F39" s="0" t="n">
-        <v>0.861279</v>
+        <v>5.497374</v>
       </c>
       <c r="G39" s="0" t="n">
-        <v>0.044558</v>
+        <v>1.326343</v>
       </c>
       <c r="H39" s="0" t="n">
-        <v>2.678099</v>
+        <v>1.294198</v>
       </c>
       <c r="I39" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>0.6799587875893454</v>
+        <v>0.7021092928936763</v>
       </c>
       <c r="K39" s="0" t="n">
-        <v>0.292199</v>
+        <v>79.12683</v>
       </c>
       <c r="L39" s="0" t="n">
-        <v>0.6799587875893454</v>
+        <v>0.7021092928936763</v>
       </c>
       <c r="M39" s="0" t="inlineStr"/>
       <c r="N39" s="0" t="n">
@@ -43072,43 +42874,43 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(2)</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C40" s="0" t="n">
-        <v>3.200128</v>
+        <v>0.200128</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.116832</v>
+        <v>4.500017</v>
       </c>
       <c r="E40" s="0" t="n">
-        <v>16.579986</v>
+        <v>2.908322</v>
       </c>
       <c r="F40" s="0" t="n">
-        <v>0.861279</v>
+        <v>0.409538</v>
       </c>
       <c r="G40" s="0" t="n">
-        <v>0.041386</v>
+        <v>1.107365</v>
       </c>
       <c r="H40" s="0" t="n">
-        <v>2.494667</v>
+        <v>1.263218</v>
       </c>
       <c r="I40" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>0.6795253086866808</v>
+        <v>0.7692935499906738</v>
       </c>
       <c r="K40" s="0" t="n">
-        <v>0.249594</v>
+        <v>5.70926</v>
       </c>
       <c r="L40" s="0" t="n">
-        <v>0.6795253086866808</v>
+        <v>0.7692935499906738</v>
       </c>
       <c r="M40" s="0" t="inlineStr"/>
       <c r="N40" s="0" t="n">
@@ -43118,45 +42920,36 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(3)</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C41" s="0" t="n">
-        <v>3.200128</v>
-      </c>
-      <c r="D41" s="0" t="n">
-        <v>0.125713</v>
-      </c>
-      <c r="E41" s="0" t="n">
-        <v>16.584694</v>
-      </c>
-      <c r="F41" s="0" t="n">
-        <v>0.861279</v>
-      </c>
-      <c r="G41" s="0" t="n">
-        <v>0.040991</v>
-      </c>
-      <c r="H41" s="0" t="n">
-        <v>2.498529</v>
-      </c>
-      <c r="I41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="0" t="n">
-        <v>0.679789881625394</v>
-      </c>
+        <v>0.200128</v>
+      </c>
+      <c r="D41" s="0" t="inlineStr"/>
+      <c r="E41" s="0" t="inlineStr"/>
+      <c r="F41" s="0" t="inlineStr"/>
+      <c r="G41" s="0" t="inlineStr"/>
+      <c r="H41" s="0" t="inlineStr"/>
+      <c r="I41" s="0" t="inlineStr"/>
+      <c r="J41" s="0" t="inlineStr"/>
       <c r="K41" s="0" t="n">
-        <v>0.265026</v>
+        <v>0.137427</v>
       </c>
       <c r="L41" s="0" t="n">
-        <v>0.679789881625394</v>
-      </c>
-      <c r="M41" s="0" t="inlineStr"/>
+        <v>0.4340007147880677</v>
+      </c>
+      <c r="M41" s="0" t="inlineStr">
+        <is>
+          <t>RuntimeError: Error(s) in loading state_dict for GPT2LMHeadModel:
+	size mismatch for transformer.wte.weight: copying a param with shape torch.Size([386, 768]) from checkpoint, the shape in current model is torch.Size([2739, 768]).</t>
+        </is>
+      </c>
       <c r="N41" s="0" t="n">
         <v>0</v>
       </c>
@@ -43164,181 +42957,181 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C42" s="0" t="n">
-        <v>255.645408</v>
+        <v>0.200128</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>40248.181123</v>
+        <v>19.352581</v>
       </c>
       <c r="E42" s="0" t="n">
-        <v>3483.221779</v>
+        <v>15.850755</v>
       </c>
       <c r="F42" s="0" t="n">
-        <v>7.503442</v>
+        <v>1.099663</v>
       </c>
       <c r="G42" s="0" t="n">
-        <v>46.234079</v>
+        <v>1.095743</v>
       </c>
       <c r="H42" s="0" t="n">
-        <v>78.58078099999999</v>
+        <v>1.256822</v>
       </c>
       <c r="I42" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>0.9396237508326822</v>
+        <v>0.686746928731073</v>
       </c>
       <c r="K42" s="0" t="n">
-        <v>40294.506578</v>
+        <v>20.550202</v>
       </c>
       <c r="L42" s="0" t="n">
-        <v>0.9396237508326822</v>
+        <v>0.686746928731073</v>
       </c>
       <c r="M42" s="0" t="inlineStr"/>
       <c r="N42" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>ColumnSynthesizer</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>expedia_hotel_logs</t>
         </is>
       </c>
       <c r="C43" s="0" t="n">
-        <v>255.645408</v>
+        <v>0.200128</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>62.498895</v>
+        <v>0.181819</v>
       </c>
       <c r="E43" s="0" t="n">
-        <v>1287.931214</v>
+        <v>1.089203</v>
       </c>
       <c r="F43" s="0" t="n">
-        <v>255.674697</v>
+        <v>0.233522</v>
       </c>
       <c r="G43" s="0" t="n">
-        <v>1.900782</v>
+        <v>0.024487</v>
       </c>
       <c r="H43" s="0" t="n">
-        <v>3515.466492</v>
+        <v>1.428925</v>
       </c>
       <c r="I43" s="0" t="n">
-        <v>0.492734244888073</v>
+        <v>0.8347199999999999</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>0.7135732076047883</v>
+        <v>0.3104905420901955</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>64.501555</v>
+        <v>0.295383</v>
       </c>
       <c r="L43" s="0" t="n">
-        <v>0.7135732076047883</v>
+        <v>0.3104905420901955</v>
       </c>
       <c r="M43" s="0" t="inlineStr"/>
       <c r="N43" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C44" s="0" t="n">
-        <v>255.645408</v>
+        <v>3.340128</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>44676.97402</v>
+        <v>701.058734</v>
       </c>
       <c r="E44" s="0" t="n">
-        <v>3739.373886</v>
+        <v>46.788901</v>
       </c>
       <c r="F44" s="0" t="n">
-        <v>8.101912</v>
+        <v>5.835959</v>
       </c>
       <c r="G44" s="0" t="n">
-        <v>124.116482</v>
+        <v>0.98127</v>
       </c>
       <c r="H44" s="0" t="n">
-        <v>61.226681</v>
+        <v>3.933356</v>
       </c>
       <c r="I44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>0.674561704813339</v>
+        <v>0.8873949346202266</v>
       </c>
       <c r="K44" s="0" t="n">
-        <v>44801.179579</v>
+        <v>702.1313799999999</v>
       </c>
       <c r="L44" s="0" t="n">
-        <v>0.674561704813339</v>
+        <v>0.8873949346202266</v>
       </c>
       <c r="M44" s="0" t="inlineStr"/>
       <c r="N44" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>GaussianCopulaSynthesizer</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C45" s="0" t="n">
-        <v>255.645408</v>
+        <v>3.340128</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>377.064984</v>
+        <v>3.806911</v>
       </c>
       <c r="E45" s="0" t="n">
-        <v>2625.842367</v>
+        <v>21.915815</v>
       </c>
       <c r="F45" s="0" t="n">
-        <v>0.730716</v>
+        <v>3.325298</v>
       </c>
       <c r="G45" s="0" t="n">
-        <v>71.379243</v>
+        <v>0.192147</v>
       </c>
       <c r="H45" s="0" t="n">
-        <v>60.59037</v>
+        <v>3.946458</v>
       </c>
       <c r="I45" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>0.5949887839771277</v>
+        <v>0.9638086812071592</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>448.546105</v>
+        <v>4.100936</v>
       </c>
       <c r="L45" s="0" t="n">
-        <v>0.5949887839771277</v>
+        <v>0.9638086812071592</v>
       </c>
       <c r="M45" s="0" t="inlineStr"/>
       <c r="N45" s="0" t="n">
@@ -43348,33 +43141,45 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr"/>
-      <c r="D46" s="0" t="inlineStr"/>
-      <c r="E46" s="0" t="inlineStr"/>
-      <c r="F46" s="0" t="inlineStr"/>
-      <c r="G46" s="0" t="inlineStr"/>
-      <c r="H46" s="0" t="inlineStr"/>
-      <c r="I46" s="0" t="inlineStr"/>
-      <c r="J46" s="0" t="inlineStr"/>
+          <t>insurance</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>3.340128</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>721.868278</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>50.139183</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>5.836993</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>1.023689</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>3.966433</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>0.9100763104035388</v>
+      </c>
       <c r="K46" s="0" t="n">
-        <v>345600.137427</v>
+        <v>722.981044</v>
       </c>
       <c r="L46" s="0" t="n">
-        <v>0.4340007147880677</v>
-      </c>
-      <c r="M46" s="0" t="inlineStr">
-        <is>
-          <t>Synthesizer Timeout</t>
-        </is>
-      </c>
+        <v>0.9100763104035388</v>
+      </c>
+      <c r="M46" s="0" t="inlineStr"/>
       <c r="N46" s="0" t="n">
         <v>0</v>
       </c>
@@ -43382,227 +43187,218 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>TVAESynthesizer</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C47" s="0" t="n">
-        <v>255.645408</v>
+        <v>3.340128</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>21309.350192</v>
+        <v>20.211784</v>
       </c>
       <c r="E47" s="0" t="n">
-        <v>3483.232857</v>
+        <v>44.916159</v>
       </c>
       <c r="F47" s="0" t="n">
-        <v>10.32129</v>
+        <v>0.390418</v>
       </c>
       <c r="G47" s="0" t="n">
-        <v>32.411723</v>
+        <v>1.169956</v>
       </c>
       <c r="H47" s="0" t="n">
-        <v>74.74739600000001</v>
+        <v>3.957934</v>
       </c>
       <c r="I47" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>0.9573278212792348</v>
+        <v>0.9706317984770574</v>
       </c>
       <c r="K47" s="0" t="n">
-        <v>21341.863793</v>
+        <v>21.483618</v>
       </c>
       <c r="L47" s="0" t="n">
-        <v>0.9573278212792348</v>
+        <v>0.9706317984770574</v>
       </c>
       <c r="M47" s="0" t="inlineStr"/>
       <c r="N47" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C48" s="0" t="n">
-        <v>255.645408</v>
-      </c>
-      <c r="D48" s="0" t="n">
-        <v>0.92648</v>
-      </c>
-      <c r="E48" s="0" t="n">
-        <v>1287.772295</v>
-      </c>
-      <c r="F48" s="0" t="n">
-        <v>255.648398</v>
-      </c>
-      <c r="G48" s="0" t="n">
-        <v>0.524177</v>
-      </c>
-      <c r="H48" s="0" t="n">
-        <v>85.833828</v>
-      </c>
-      <c r="I48" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="0" t="n">
-        <v>0.7522036832451139</v>
-      </c>
+        <v>3.340128</v>
+      </c>
+      <c r="D48" s="0" t="inlineStr"/>
+      <c r="E48" s="0" t="inlineStr"/>
+      <c r="F48" s="0" t="inlineStr"/>
+      <c r="G48" s="0" t="inlineStr"/>
+      <c r="H48" s="0" t="inlineStr"/>
+      <c r="I48" s="0" t="inlineStr"/>
+      <c r="J48" s="0" t="inlineStr"/>
       <c r="K48" s="0" t="n">
-        <v>1.552535</v>
+        <v>0.137427</v>
       </c>
       <c r="L48" s="0" t="n">
-        <v>0.7522036832451139</v>
-      </c>
-      <c r="M48" s="0" t="inlineStr"/>
+        <v>0.4340007147880677</v>
+      </c>
+      <c r="M48" s="0" t="inlineStr">
+        <is>
+          <t>RuntimeError: Error(s) in loading state_dict for GPT2LMHeadModel:
+	size mismatch for transformer.wte.weight: copying a param with shape torch.Size([386, 768]) from checkpoint, the shape in current model is torch.Size([100, 768]).</t>
+        </is>
+      </c>
       <c r="N48" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(1)</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C49" s="0" t="n">
-        <v>255.645408</v>
+        <v>3.340128</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>0.967338</v>
+        <v>236.208372</v>
       </c>
       <c r="E49" s="0" t="n">
-        <v>1287.762884</v>
+        <v>46.782424</v>
       </c>
       <c r="F49" s="0" t="n">
-        <v>255.648398</v>
+        <v>0.988737</v>
       </c>
       <c r="G49" s="0" t="n">
-        <v>0.547588</v>
+        <v>0.75692</v>
       </c>
       <c r="H49" s="0" t="n">
-        <v>91.68889900000001</v>
+        <v>3.977989</v>
       </c>
       <c r="I49" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>0.7521850232083631</v>
+        <v>0.923786653910339</v>
       </c>
       <c r="K49" s="0" t="n">
-        <v>1.604003</v>
+        <v>237.06717</v>
       </c>
       <c r="L49" s="0" t="n">
-        <v>0.7521850232083631</v>
+        <v>0.923786653910339</v>
       </c>
       <c r="M49" s="0" t="inlineStr"/>
       <c r="N49" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(2)</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C50" s="0" t="n">
-        <v>255.645408</v>
+        <v>3.340128</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>0.911209</v>
+        <v>0.14459</v>
       </c>
       <c r="E50" s="0" t="n">
-        <v>1287.763434</v>
+        <v>17.165133</v>
       </c>
       <c r="F50" s="0" t="n">
-        <v>255.648398</v>
+        <v>1.147901</v>
       </c>
       <c r="G50" s="0" t="n">
-        <v>0.5350200000000001</v>
+        <v>0.047561</v>
       </c>
       <c r="H50" s="0" t="n">
-        <v>89.788228</v>
+        <v>3.963101</v>
       </c>
       <c r="I50" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>0.752204260906699</v>
+        <v>0.6075051224656985</v>
       </c>
       <c r="K50" s="0" t="n">
-        <v>1.537605</v>
+        <v>0.281228</v>
       </c>
       <c r="L50" s="0" t="n">
-        <v>0.752204260906699</v>
+        <v>0.6075051224656985</v>
       </c>
       <c r="M50" s="0" t="inlineStr"/>
       <c r="N50" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(3)</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>covtype</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C51" s="0" t="n">
-        <v>255.645408</v>
+        <v>162.039016</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>0.931684</v>
+        <v>31745.518702</v>
       </c>
       <c r="E51" s="0" t="n">
-        <v>16664.662708</v>
+        <v>2657.259821</v>
       </c>
       <c r="F51" s="0" t="n">
-        <v>255.648398</v>
+        <v>18.395134</v>
       </c>
       <c r="G51" s="0" t="n">
-        <v>0.741356</v>
+        <v>43.211308</v>
       </c>
       <c r="H51" s="0" t="n">
-        <v>93.19099300000001</v>
+        <v>34.51449</v>
       </c>
       <c r="I51" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>0.7521895807828693</v>
+        <v>0.7820074432198264</v>
       </c>
       <c r="K51" s="0" t="n">
-        <v>1.771362</v>
+        <v>31788.821386</v>
       </c>
       <c r="L51" s="0" t="n">
-        <v>0.7521895807828693</v>
+        <v>0.7820074432198264</v>
       </c>
       <c r="M51" s="0" t="inlineStr"/>
       <c r="N51" s="0" t="n">
@@ -43612,89 +43408,89 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C52" s="0" t="n">
-        <v>0.200128</v>
+        <v>162.039016</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>72.156249</v>
+        <v>49.068304</v>
       </c>
       <c r="E52" s="0" t="n">
-        <v>16.143328</v>
+        <v>790.719489</v>
       </c>
       <c r="F52" s="0" t="n">
-        <v>5.425123</v>
+        <v>150.213244</v>
       </c>
       <c r="G52" s="0" t="n">
-        <v>1.182253</v>
+        <v>1.195148</v>
       </c>
       <c r="H52" s="0" t="n">
-        <v>1.252887</v>
+        <v>51.83014</v>
       </c>
       <c r="I52" s="0" t="n">
-        <v>1</v>
+        <v>0.5256410256410257</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>0.6957054551909917</v>
+        <v>0.7588336912052365</v>
       </c>
       <c r="K52" s="0" t="n">
-        <v>73.429878</v>
+        <v>50.36533</v>
       </c>
       <c r="L52" s="0" t="n">
-        <v>0.6957054551909917</v>
+        <v>0.7588336912052365</v>
       </c>
       <c r="M52" s="0" t="inlineStr"/>
       <c r="N52" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>ColumnSynthesizer</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C53" s="0" t="n">
-        <v>0.200128</v>
+        <v>162.039016</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>0.54053</v>
+        <v>34768.849675</v>
       </c>
       <c r="E53" s="0" t="n">
-        <v>1.181518</v>
+        <v>2961.945932</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>0.24771</v>
+        <v>18.840029</v>
       </c>
       <c r="G53" s="0" t="n">
-        <v>0.042428</v>
+        <v>72.38010300000001</v>
       </c>
       <c r="H53" s="0" t="n">
-        <v>1.834723</v>
+        <v>31.659839</v>
       </c>
       <c r="I53" s="0" t="n">
-        <v>0.2796155555555556</v>
+        <v>1</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>0.2518450866737775</v>
+        <v>0.6119190421245482</v>
       </c>
       <c r="K53" s="0" t="n">
-        <v>0.684836</v>
+        <v>34841.318855</v>
       </c>
       <c r="L53" s="0" t="n">
-        <v>0.2518450866737775</v>
+        <v>0.6119190421245482</v>
       </c>
       <c r="M53" s="0" t="inlineStr"/>
       <c r="N53" s="0" t="n">
@@ -43704,43 +43500,43 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C54" s="0" t="n">
-        <v>0.200128</v>
+        <v>162.039016</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>77.71141</v>
+        <v>260.624879</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>16.514218</v>
+        <v>1665.529039</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>5.497374</v>
+        <v>0.568125</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>1.326343</v>
+        <v>35.885013</v>
       </c>
       <c r="H54" s="0" t="n">
-        <v>1.294198</v>
+        <v>32.917708</v>
       </c>
       <c r="I54" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>0.7021092928936763</v>
+        <v>0.6896156174865535</v>
       </c>
       <c r="K54" s="0" t="n">
-        <v>79.12683</v>
+        <v>296.61177</v>
       </c>
       <c r="L54" s="0" t="n">
-        <v>0.7021092928936763</v>
+        <v>0.6896156174865535</v>
       </c>
       <c r="M54" s="0" t="inlineStr"/>
       <c r="N54" s="0" t="n">
@@ -43750,45 +43546,35 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>GaussianCopulaSynthesizer</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C55" s="0" t="n">
-        <v>0.200128</v>
-      </c>
-      <c r="D55" s="0" t="n">
-        <v>4.500017</v>
-      </c>
-      <c r="E55" s="0" t="n">
-        <v>2.908322</v>
-      </c>
-      <c r="F55" s="0" t="n">
-        <v>0.409538</v>
-      </c>
-      <c r="G55" s="0" t="n">
-        <v>1.107365</v>
-      </c>
-      <c r="H55" s="0" t="n">
-        <v>1.263218</v>
-      </c>
-      <c r="I55" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="0" t="n">
-        <v>0.7692935499906738</v>
-      </c>
+        <v>162.039016</v>
+      </c>
+      <c r="D55" s="0" t="inlineStr"/>
+      <c r="E55" s="0" t="inlineStr"/>
+      <c r="F55" s="0" t="inlineStr"/>
+      <c r="G55" s="0" t="inlineStr"/>
+      <c r="H55" s="0" t="inlineStr"/>
+      <c r="I55" s="0" t="inlineStr"/>
+      <c r="J55" s="0" t="inlineStr"/>
       <c r="K55" s="0" t="n">
-        <v>5.70926</v>
+        <v>0.137427</v>
       </c>
       <c r="L55" s="0" t="n">
-        <v>0.7692935499906738</v>
-      </c>
-      <c r="M55" s="0" t="inlineStr"/>
+        <v>0.4340007147880677</v>
+      </c>
+      <c r="M55" s="0" t="inlineStr">
+        <is>
+          <t>RuntimeError: Parent directory rtf_checkpoints/checkpoint-16500 does not exist.</t>
+        </is>
+      </c>
       <c r="N55" s="0" t="n">
         <v>0</v>
       </c>
@@ -43796,80 +43582,89 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>RealTabFormerSynthesizer(3)</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C56" s="0" t="n">
-        <v>0.200128</v>
-      </c>
-      <c r="D56" s="0" t="inlineStr"/>
-      <c r="E56" s="0" t="inlineStr"/>
-      <c r="F56" s="0" t="inlineStr"/>
-      <c r="G56" s="0" t="inlineStr"/>
-      <c r="H56" s="0" t="inlineStr"/>
-      <c r="I56" s="0" t="inlineStr"/>
-      <c r="J56" s="0" t="inlineStr"/>
+        <v>162.039016</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>14943.201608</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>2657.27821</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>8.612152999999999</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>34.109669</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>37.18000300000001</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>0.8719801650843582</v>
+      </c>
       <c r="K56" s="0" t="n">
-        <v>0.137427</v>
+        <v>14977.413155</v>
       </c>
       <c r="L56" s="0" t="n">
-        <v>0.4340007147880677</v>
-      </c>
-      <c r="M56" s="0" t="inlineStr">
-        <is>
-          <t>RuntimeError: Error(s) in loading state_dict for GPT2LMHeadModel:
-	size mismatch for transformer.wte.weight: copying a param with shape torch.Size([386, 768]) from checkpoint, the shape in current model is torch.Size([2739, 768]).</t>
-        </is>
-      </c>
+        <v>0.8719801650843582</v>
+      </c>
+      <c r="M56" s="0" t="inlineStr"/>
       <c r="N56" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>TVAESynthesizer</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>intrusion</t>
         </is>
       </c>
       <c r="C57" s="0" t="n">
-        <v>0.200128</v>
+        <v>162.039016</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>19.352581</v>
+        <v>0.743468</v>
       </c>
       <c r="E57" s="0" t="n">
-        <v>15.850755</v>
+        <v>790.620308</v>
       </c>
       <c r="F57" s="0" t="n">
-        <v>1.099663</v>
+        <v>150.190464</v>
       </c>
       <c r="G57" s="0" t="n">
-        <v>1.095743</v>
+        <v>0.463446</v>
       </c>
       <c r="H57" s="0" t="n">
-        <v>1.256822</v>
+        <v>43.762349</v>
       </c>
       <c r="I57" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>0.686746928731073</v>
+        <v>0.603420933256513</v>
       </c>
       <c r="K57" s="0" t="n">
-        <v>20.550202</v>
+        <v>1.295991</v>
       </c>
       <c r="L57" s="0" t="n">
-        <v>0.686746928731073</v>
+        <v>0.603420933256513</v>
       </c>
       <c r="M57" s="0" t="inlineStr"/>
       <c r="N57" s="0" t="n">
@@ -43879,89 +43674,89 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer</t>
+          <t>CTGANSynthesizer</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C58" s="0" t="n">
-        <v>0.200128</v>
+        <v>18.712096</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>0.194398</v>
+        <v>1844.177537</v>
       </c>
       <c r="E58" s="0" t="n">
-        <v>1.087248</v>
+        <v>272.175024</v>
       </c>
       <c r="F58" s="0" t="n">
-        <v>0.233522</v>
+        <v>3.065492</v>
       </c>
       <c r="G58" s="0" t="n">
-        <v>0.026076</v>
+        <v>3.629095</v>
       </c>
       <c r="H58" s="0" t="n">
-        <v>1.417521</v>
+        <v>11.48383</v>
       </c>
       <c r="I58" s="0" t="n">
-        <v>0.83494</v>
+        <v>1</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>0.312683297584008</v>
+        <v>0.9585146392039854</v>
       </c>
       <c r="K58" s="0" t="n">
-        <v>0.3223519999999999</v>
+        <v>1847.898008</v>
       </c>
       <c r="L58" s="0" t="n">
-        <v>0.312683297584008</v>
+        <v>0.9585146392039854</v>
       </c>
       <c r="M58" s="0" t="inlineStr"/>
       <c r="N58" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(1)</t>
+          <t>ColumnSynthesizer</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C59" s="0" t="n">
-        <v>0.200128</v>
+        <v>18.712096</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>0.181819</v>
+        <v>15.802105</v>
       </c>
       <c r="E59" s="0" t="n">
-        <v>1.089203</v>
+        <v>94.614374</v>
       </c>
       <c r="F59" s="0" t="n">
-        <v>0.233522</v>
+        <v>18.751844</v>
       </c>
       <c r="G59" s="0" t="n">
-        <v>0.024487</v>
+        <v>0.224436</v>
       </c>
       <c r="H59" s="0" t="n">
-        <v>1.428925</v>
+        <v>13.893226</v>
       </c>
       <c r="I59" s="0" t="n">
-        <v>0.8347199999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>0.3104905420901955</v>
+        <v>0.8105251658089374</v>
       </c>
       <c r="K59" s="0" t="n">
-        <v>0.295383</v>
+        <v>16.128419</v>
       </c>
       <c r="L59" s="0" t="n">
-        <v>0.3104905420901955</v>
+        <v>0.8105251658089374</v>
       </c>
       <c r="M59" s="0" t="inlineStr"/>
       <c r="N59" s="0" t="n">
@@ -43971,89 +43766,89 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(2)</t>
+          <t>CopulaGANSynthesizer</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C60" s="0" t="n">
-        <v>0.200128</v>
+        <v>18.712096</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>0.202544</v>
+        <v>2005.126063</v>
       </c>
       <c r="E60" s="0" t="n">
-        <v>1.090063</v>
+        <v>320.959614</v>
       </c>
       <c r="F60" s="0" t="n">
-        <v>0.233522</v>
+        <v>3.796645</v>
       </c>
       <c r="G60" s="0" t="n">
-        <v>0.024747</v>
+        <v>7.843599</v>
       </c>
       <c r="H60" s="0" t="n">
-        <v>1.408316</v>
+        <v>11.339986</v>
       </c>
       <c r="I60" s="0" t="n">
-        <v>0.83462</v>
+        <v>1</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>0.3094455978002973</v>
+        <v>0.924008248697574</v>
       </c>
       <c r="K60" s="0" t="n">
-        <v>0.318667</v>
+        <v>2013.058739</v>
       </c>
       <c r="L60" s="0" t="n">
-        <v>0.3094455978002973</v>
+        <v>0.924008248697574</v>
       </c>
       <c r="M60" s="0" t="inlineStr"/>
       <c r="N60" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t>UniformSynthesizer(3)</t>
+          <t>GaussianCopulaSynthesizer</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>expedia_hotel_logs</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C61" s="0" t="n">
-        <v>0.200128</v>
+        <v>18.712096</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>0.209525</v>
+        <v>42.389287</v>
       </c>
       <c r="E61" s="0" t="n">
-        <v>183.724163</v>
+        <v>193.004936</v>
       </c>
       <c r="F61" s="0" t="n">
-        <v>0.233522</v>
+        <v>0.780758</v>
       </c>
       <c r="G61" s="0" t="n">
-        <v>0.036029</v>
+        <v>4.734066</v>
       </c>
       <c r="H61" s="0" t="n">
-        <v>1.521223</v>
+        <v>10.4996</v>
       </c>
       <c r="I61" s="0" t="n">
-        <v>0.8354200000000001</v>
+        <v>1</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>0.3123482730828604</v>
+        <v>0.8689819291242673</v>
       </c>
       <c r="K61" s="0" t="n">
-        <v>0.3438759999999999</v>
+        <v>47.225231</v>
       </c>
       <c r="L61" s="0" t="n">
-        <v>0.3123482730828604</v>
+        <v>0.8689819291242673</v>
       </c>
       <c r="M61" s="0" t="inlineStr"/>
       <c r="N61" s="0" t="n">
@@ -44063,45 +43858,36 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t>CTGANSynthesizer(2)</t>
+          <t>RealTabFormerSynthesizer</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C62" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D62" s="0" t="n">
-        <v>701.058734</v>
-      </c>
-      <c r="E62" s="0" t="n">
-        <v>46.788901</v>
-      </c>
-      <c r="F62" s="0" t="n">
-        <v>5.835959</v>
-      </c>
-      <c r="G62" s="0" t="n">
-        <v>0.98127</v>
-      </c>
-      <c r="H62" s="0" t="n">
-        <v>3.933356</v>
-      </c>
-      <c r="I62" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="0" t="n">
-        <v>0.8873949346202266</v>
-      </c>
+        <v>18.712096</v>
+      </c>
+      <c r="D62" s="0" t="inlineStr"/>
+      <c r="E62" s="0" t="inlineStr"/>
+      <c r="F62" s="0" t="inlineStr"/>
+      <c r="G62" s="0" t="inlineStr"/>
+      <c r="H62" s="0" t="inlineStr"/>
+      <c r="I62" s="0" t="inlineStr"/>
+      <c r="J62" s="0" t="inlineStr"/>
       <c r="K62" s="0" t="n">
-        <v>702.1313799999999</v>
+        <v>0.137427</v>
       </c>
       <c r="L62" s="0" t="n">
-        <v>0.8873949346202266</v>
-      </c>
-      <c r="M62" s="0" t="inlineStr"/>
+        <v>0.4340007147880677</v>
+      </c>
+      <c r="M62" s="0" t="inlineStr">
+        <is>
+          <t>RuntimeError: Error(s) in loading state_dict for GPT2LMHeadModel:
+	size mismatch for transformer.wte.weight: copying a param with shape torch.Size([386, 768]) from checkpoint, the shape in current model is torch.Size([891, 768]).</t>
+        </is>
+      </c>
       <c r="N62" s="0" t="n">
         <v>0</v>
       </c>
@@ -44109,1306 +43895,92 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>ColumnSynthesizer</t>
+          <t>TVAESynthesizer</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C63" s="0" t="n">
-        <v>3.340128</v>
+        <v>18.712096</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>3.806911</v>
+        <v>1425.108941</v>
       </c>
       <c r="E63" s="0" t="n">
-        <v>21.915815</v>
+        <v>272.188011</v>
       </c>
       <c r="F63" s="0" t="n">
-        <v>3.325298</v>
+        <v>2.687627</v>
       </c>
       <c r="G63" s="0" t="n">
-        <v>0.192147</v>
+        <v>2.631622</v>
       </c>
       <c r="H63" s="0" t="n">
-        <v>3.946458</v>
+        <v>9.657814</v>
       </c>
       <c r="I63" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>0.9638086812071592</v>
+        <v>0.9332505991219198</v>
       </c>
       <c r="K63" s="0" t="n">
-        <v>4.100936</v>
+        <v>1427.842441</v>
       </c>
       <c r="L63" s="0" t="n">
-        <v>0.9638086812071592</v>
+        <v>0.9332505991219198</v>
       </c>
       <c r="M63" s="0" t="inlineStr"/>
       <c r="N63" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>CopulaGANSynthesizer(1)</t>
+          <t>UniformSynthesizer</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C64" s="0" t="n">
-        <v>3.340128</v>
+        <v>18.712096</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>721.868278</v>
+        <v>0.25967</v>
       </c>
       <c r="E64" s="0" t="n">
-        <v>50.139183</v>
+        <v>94.46084999999999</v>
       </c>
       <c r="F64" s="0" t="n">
-        <v>5.836993</v>
+        <v>18.715492</v>
       </c>
       <c r="G64" s="0" t="n">
-        <v>1.023689</v>
+        <v>0.077821</v>
       </c>
       <c r="H64" s="0" t="n">
-        <v>3.966433</v>
+        <v>12.683264</v>
       </c>
       <c r="I64" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>0.9100763104035388</v>
+        <v>0.7405637769330489</v>
       </c>
       <c r="K64" s="0" t="n">
-        <v>722.981044</v>
+        <v>0.426568</v>
       </c>
       <c r="L64" s="0" t="n">
-        <v>0.9100763104035388</v>
+        <v>0.7405637769330489</v>
       </c>
       <c r="M64" s="0" t="inlineStr"/>
       <c r="N64" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="inlineStr">
-        <is>
-          <t>GaussianCopulaSynthesizer</t>
-        </is>
-      </c>
-      <c r="B65" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D65" s="0" t="n">
-        <v>20.211784</v>
-      </c>
-      <c r="E65" s="0" t="n">
-        <v>44.916159</v>
-      </c>
-      <c r="F65" s="0" t="n">
-        <v>0.390418</v>
-      </c>
-      <c r="G65" s="0" t="n">
-        <v>1.169956</v>
-      </c>
-      <c r="H65" s="0" t="n">
-        <v>3.957934</v>
-      </c>
-      <c r="I65" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="0" t="n">
-        <v>0.9706317984770574</v>
-      </c>
-      <c r="K65" s="0" t="n">
-        <v>21.483618</v>
-      </c>
-      <c r="L65" s="0" t="n">
-        <v>0.9706317984770574</v>
-      </c>
-      <c r="M65" s="0" t="inlineStr"/>
-      <c r="N65" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="inlineStr">
-        <is>
-          <t>RealTabFormerSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B66" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C66" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D66" s="0" t="inlineStr"/>
-      <c r="E66" s="0" t="inlineStr"/>
-      <c r="F66" s="0" t="inlineStr"/>
-      <c r="G66" s="0" t="inlineStr"/>
-      <c r="H66" s="0" t="inlineStr"/>
-      <c r="I66" s="0" t="inlineStr"/>
-      <c r="J66" s="0" t="inlineStr"/>
-      <c r="K66" s="0" t="n">
-        <v>0.137427</v>
-      </c>
-      <c r="L66" s="0" t="n">
-        <v>0.4340007147880677</v>
-      </c>
-      <c r="M66" s="0" t="inlineStr">
-        <is>
-          <t>RuntimeError: Error(s) in loading state_dict for GPT2LMHeadModel:
-	size mismatch for transformer.wte.weight: copying a param with shape torch.Size([386, 768]) from checkpoint, the shape in current model is torch.Size([100, 768]).</t>
-        </is>
-      </c>
-      <c r="N66" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="inlineStr">
-        <is>
-          <t>TVAESynthesizer</t>
-        </is>
-      </c>
-      <c r="B67" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D67" s="0" t="n">
-        <v>236.208372</v>
-      </c>
-      <c r="E67" s="0" t="n">
-        <v>46.782424</v>
-      </c>
-      <c r="F67" s="0" t="n">
-        <v>0.988737</v>
-      </c>
-      <c r="G67" s="0" t="n">
-        <v>0.75692</v>
-      </c>
-      <c r="H67" s="0" t="n">
-        <v>3.977989</v>
-      </c>
-      <c r="I67" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="0" t="n">
-        <v>0.923786653910339</v>
-      </c>
-      <c r="K67" s="0" t="n">
-        <v>237.06717</v>
-      </c>
-      <c r="L67" s="0" t="n">
-        <v>0.923786653910339</v>
-      </c>
-      <c r="M67" s="0" t="inlineStr"/>
-      <c r="N67" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer</t>
-        </is>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D68" s="0" t="n">
-        <v>0.146041</v>
-      </c>
-      <c r="E68" s="0" t="n">
-        <v>17.176417</v>
-      </c>
-      <c r="F68" s="0" t="n">
-        <v>1.147901</v>
-      </c>
-      <c r="G68" s="0" t="n">
-        <v>0.046539</v>
-      </c>
-      <c r="H68" s="0" t="n">
-        <v>3.906893</v>
-      </c>
-      <c r="I68" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="0" t="n">
-        <v>0.6074403974551235</v>
-      </c>
-      <c r="K68" s="0" t="n">
-        <v>0.294458</v>
-      </c>
-      <c r="L68" s="0" t="n">
-        <v>0.6074403974551235</v>
-      </c>
-      <c r="M68" s="0" t="inlineStr"/>
-      <c r="N68" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(1)</t>
-        </is>
-      </c>
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D69" s="0" t="n">
-        <v>0.14459</v>
-      </c>
-      <c r="E69" s="0" t="n">
-        <v>17.165133</v>
-      </c>
-      <c r="F69" s="0" t="n">
-        <v>1.147901</v>
-      </c>
-      <c r="G69" s="0" t="n">
-        <v>0.047561</v>
-      </c>
-      <c r="H69" s="0" t="n">
-        <v>3.963101</v>
-      </c>
-      <c r="I69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="0" t="n">
-        <v>0.6075051224656985</v>
-      </c>
-      <c r="K69" s="0" t="n">
-        <v>0.281228</v>
-      </c>
-      <c r="L69" s="0" t="n">
-        <v>0.6075051224656985</v>
-      </c>
-      <c r="M69" s="0" t="inlineStr"/>
-      <c r="N69" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(2)</t>
-        </is>
-      </c>
-      <c r="B70" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C70" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D70" s="0" t="n">
-        <v>0.152341</v>
-      </c>
-      <c r="E70" s="0" t="n">
-        <v>17.173636</v>
-      </c>
-      <c r="F70" s="0" t="n">
-        <v>1.147901</v>
-      </c>
-      <c r="G70" s="0" t="n">
-        <v>0.046321</v>
-      </c>
-      <c r="H70" s="0" t="n">
-        <v>3.935043</v>
-      </c>
-      <c r="I70" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="0" t="n">
-        <v>0.607748636160919</v>
-      </c>
-      <c r="K70" s="0" t="n">
-        <v>0.290038</v>
-      </c>
-      <c r="L70" s="0" t="n">
-        <v>0.607748636160919</v>
-      </c>
-      <c r="M70" s="0" t="inlineStr"/>
-      <c r="N70" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C71" s="0" t="n">
-        <v>3.340128</v>
-      </c>
-      <c r="D71" s="0" t="n">
-        <v>0.194387</v>
-      </c>
-      <c r="E71" s="0" t="n">
-        <v>731.917602</v>
-      </c>
-      <c r="F71" s="0" t="n">
-        <v>1.147901</v>
-      </c>
-      <c r="G71" s="0" t="n">
-        <v>0.08422399999999999</v>
-      </c>
-      <c r="H71" s="0" t="n">
-        <v>4.286789000000001</v>
-      </c>
-      <c r="I71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="0" t="n">
-        <v>0.6058830569287348</v>
-      </c>
-      <c r="K71" s="0" t="n">
-        <v>0.3769329999999999</v>
-      </c>
-      <c r="L71" s="0" t="n">
-        <v>0.6058830569287348</v>
-      </c>
-      <c r="M71" s="0" t="inlineStr"/>
-      <c r="N71" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="inlineStr">
-        <is>
-          <t>CTGANSynthesizer(2)</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C72" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D72" s="0" t="n">
-        <v>31745.518702</v>
-      </c>
-      <c r="E72" s="0" t="n">
-        <v>2657.259821</v>
-      </c>
-      <c r="F72" s="0" t="n">
-        <v>18.395134</v>
-      </c>
-      <c r="G72" s="0" t="n">
-        <v>43.211308</v>
-      </c>
-      <c r="H72" s="0" t="n">
-        <v>34.51449</v>
-      </c>
-      <c r="I72" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="0" t="n">
-        <v>0.7820074432198264</v>
-      </c>
-      <c r="K72" s="0" t="n">
-        <v>31788.821386</v>
-      </c>
-      <c r="L72" s="0" t="n">
-        <v>0.7820074432198264</v>
-      </c>
-      <c r="M72" s="0" t="inlineStr"/>
-      <c r="N72" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="inlineStr">
-        <is>
-          <t>ColumnSynthesizer</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C73" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D73" s="0" t="n">
-        <v>49.068304</v>
-      </c>
-      <c r="E73" s="0" t="n">
-        <v>790.719489</v>
-      </c>
-      <c r="F73" s="0" t="n">
-        <v>150.213244</v>
-      </c>
-      <c r="G73" s="0" t="n">
-        <v>1.195148</v>
-      </c>
-      <c r="H73" s="0" t="n">
-        <v>51.83014</v>
-      </c>
-      <c r="I73" s="0" t="n">
-        <v>0.5256410256410257</v>
-      </c>
-      <c r="J73" s="0" t="n">
-        <v>0.7588336912052365</v>
-      </c>
-      <c r="K73" s="0" t="n">
-        <v>50.36533</v>
-      </c>
-      <c r="L73" s="0" t="n">
-        <v>0.7588336912052365</v>
-      </c>
-      <c r="M73" s="0" t="inlineStr"/>
-      <c r="N73" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t>CopulaGANSynthesizer(1)</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D74" s="0" t="n">
-        <v>34768.849675</v>
-      </c>
-      <c r="E74" s="0" t="n">
-        <v>2961.945932</v>
-      </c>
-      <c r="F74" s="0" t="n">
-        <v>18.840029</v>
-      </c>
-      <c r="G74" s="0" t="n">
-        <v>72.38010300000001</v>
-      </c>
-      <c r="H74" s="0" t="n">
-        <v>31.659839</v>
-      </c>
-      <c r="I74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="0" t="n">
-        <v>0.6119190421245482</v>
-      </c>
-      <c r="K74" s="0" t="n">
-        <v>34841.318855</v>
-      </c>
-      <c r="L74" s="0" t="n">
-        <v>0.6119190421245482</v>
-      </c>
-      <c r="M74" s="0" t="inlineStr"/>
-      <c r="N74" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="inlineStr">
-        <is>
-          <t>GaussianCopulaSynthesizer</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D75" s="0" t="n">
-        <v>260.624879</v>
-      </c>
-      <c r="E75" s="0" t="n">
-        <v>1665.529039</v>
-      </c>
-      <c r="F75" s="0" t="n">
-        <v>0.568125</v>
-      </c>
-      <c r="G75" s="0" t="n">
-        <v>35.885013</v>
-      </c>
-      <c r="H75" s="0" t="n">
-        <v>32.917708</v>
-      </c>
-      <c r="I75" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="0" t="n">
-        <v>0.6896156174865535</v>
-      </c>
-      <c r="K75" s="0" t="n">
-        <v>296.61177</v>
-      </c>
-      <c r="L75" s="0" t="n">
-        <v>0.6896156174865535</v>
-      </c>
-      <c r="M75" s="0" t="inlineStr"/>
-      <c r="N75" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="inlineStr">
-        <is>
-          <t>RealTabFormerSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D76" s="0" t="inlineStr"/>
-      <c r="E76" s="0" t="inlineStr"/>
-      <c r="F76" s="0" t="inlineStr"/>
-      <c r="G76" s="0" t="inlineStr"/>
-      <c r="H76" s="0" t="inlineStr"/>
-      <c r="I76" s="0" t="inlineStr"/>
-      <c r="J76" s="0" t="inlineStr"/>
-      <c r="K76" s="0" t="n">
-        <v>0.137427</v>
-      </c>
-      <c r="L76" s="0" t="n">
-        <v>0.4340007147880677</v>
-      </c>
-      <c r="M76" s="0" t="inlineStr">
-        <is>
-          <t>RuntimeError: Parent directory rtf_checkpoints/checkpoint-16500 does not exist.</t>
-        </is>
-      </c>
-      <c r="N76" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="inlineStr">
-        <is>
-          <t>TVAESynthesizer</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C77" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D77" s="0" t="n">
-        <v>14943.201608</v>
-      </c>
-      <c r="E77" s="0" t="n">
-        <v>2657.27821</v>
-      </c>
-      <c r="F77" s="0" t="n">
-        <v>8.612152999999999</v>
-      </c>
-      <c r="G77" s="0" t="n">
-        <v>34.109669</v>
-      </c>
-      <c r="H77" s="0" t="n">
-        <v>37.18000300000001</v>
-      </c>
-      <c r="I77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="0" t="n">
-        <v>0.8719801650843582</v>
-      </c>
-      <c r="K77" s="0" t="n">
-        <v>14977.413155</v>
-      </c>
-      <c r="L77" s="0" t="n">
-        <v>0.8719801650843582</v>
-      </c>
-      <c r="M77" s="0" t="inlineStr"/>
-      <c r="N77" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C78" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D78" s="0" t="n">
-        <v>0.750398</v>
-      </c>
-      <c r="E78" s="0" t="n">
-        <v>790.620372</v>
-      </c>
-      <c r="F78" s="0" t="n">
-        <v>150.190464</v>
-      </c>
-      <c r="G78" s="0" t="n">
-        <v>0.45833</v>
-      </c>
-      <c r="H78" s="0" t="n">
-        <v>42.006197</v>
-      </c>
-      <c r="I78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="0" t="n">
-        <v>0.6033581709365829</v>
-      </c>
-      <c r="K78" s="0" t="n">
-        <v>1.310606</v>
-      </c>
-      <c r="L78" s="0" t="n">
-        <v>0.6033581709365829</v>
-      </c>
-      <c r="M78" s="0" t="inlineStr"/>
-      <c r="N78" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(1)</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C79" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D79" s="0" t="n">
-        <v>0.743468</v>
-      </c>
-      <c r="E79" s="0" t="n">
-        <v>790.620308</v>
-      </c>
-      <c r="F79" s="0" t="n">
-        <v>150.190464</v>
-      </c>
-      <c r="G79" s="0" t="n">
-        <v>0.463446</v>
-      </c>
-      <c r="H79" s="0" t="n">
-        <v>43.762349</v>
-      </c>
-      <c r="I79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="0" t="n">
-        <v>0.603420933256513</v>
-      </c>
-      <c r="K79" s="0" t="n">
-        <v>1.295991</v>
-      </c>
-      <c r="L79" s="0" t="n">
-        <v>0.603420933256513</v>
-      </c>
-      <c r="M79" s="0" t="inlineStr"/>
-      <c r="N79" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(2)</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C80" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D80" s="0" t="n">
-        <v>0.760941</v>
-      </c>
-      <c r="E80" s="0" t="n">
-        <v>790.621414</v>
-      </c>
-      <c r="F80" s="0" t="n">
-        <v>150.190464</v>
-      </c>
-      <c r="G80" s="0" t="n">
-        <v>0.466698</v>
-      </c>
-      <c r="H80" s="0" t="n">
-        <v>43.864252</v>
-      </c>
-      <c r="I80" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="0" t="n">
-        <v>0.6032219205693424</v>
-      </c>
-      <c r="K80" s="0" t="n">
-        <v>1.319015</v>
-      </c>
-      <c r="L80" s="0" t="n">
-        <v>0.6032219205693424</v>
-      </c>
-      <c r="M80" s="0" t="inlineStr"/>
-      <c r="N80" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B81" s="0" t="inlineStr">
-        <is>
-          <t>intrusion</t>
-        </is>
-      </c>
-      <c r="C81" s="0" t="n">
-        <v>162.039016</v>
-      </c>
-      <c r="D81" s="0" t="n">
-        <v>0.74021</v>
-      </c>
-      <c r="E81" s="0" t="n">
-        <v>12396.8782</v>
-      </c>
-      <c r="F81" s="0" t="n">
-        <v>150.190464</v>
-      </c>
-      <c r="G81" s="0" t="n">
-        <v>0.479107</v>
-      </c>
-      <c r="H81" s="0" t="n">
-        <v>46.011103</v>
-      </c>
-      <c r="I81" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="0" t="n">
-        <v>0.6033510994961839</v>
-      </c>
-      <c r="K81" s="0" t="n">
-        <v>1.317639</v>
-      </c>
-      <c r="L81" s="0" t="n">
-        <v>0.6033510994961839</v>
-      </c>
-      <c r="M81" s="0" t="inlineStr"/>
-      <c r="N81" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="inlineStr">
-        <is>
-          <t>CTGANSynthesizer(2)</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C82" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D82" s="0" t="n">
-        <v>1844.177537</v>
-      </c>
-      <c r="E82" s="0" t="n">
-        <v>272.175024</v>
-      </c>
-      <c r="F82" s="0" t="n">
-        <v>3.065492</v>
-      </c>
-      <c r="G82" s="0" t="n">
-        <v>3.629095</v>
-      </c>
-      <c r="H82" s="0" t="n">
-        <v>11.48383</v>
-      </c>
-      <c r="I82" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="0" t="n">
-        <v>0.9585146392039854</v>
-      </c>
-      <c r="K82" s="0" t="n">
-        <v>1847.898008</v>
-      </c>
-      <c r="L82" s="0" t="n">
-        <v>0.9585146392039854</v>
-      </c>
-      <c r="M82" s="0" t="inlineStr"/>
-      <c r="N82" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="inlineStr">
-        <is>
-          <t>ColumnSynthesizer</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C83" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D83" s="0" t="n">
-        <v>15.802105</v>
-      </c>
-      <c r="E83" s="0" t="n">
-        <v>94.614374</v>
-      </c>
-      <c r="F83" s="0" t="n">
-        <v>18.751844</v>
-      </c>
-      <c r="G83" s="0" t="n">
-        <v>0.224436</v>
-      </c>
-      <c r="H83" s="0" t="n">
-        <v>13.893226</v>
-      </c>
-      <c r="I83" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J83" s="0" t="n">
-        <v>0.8105251658089374</v>
-      </c>
-      <c r="K83" s="0" t="n">
-        <v>16.128419</v>
-      </c>
-      <c r="L83" s="0" t="n">
-        <v>0.8105251658089374</v>
-      </c>
-      <c r="M83" s="0" t="inlineStr"/>
-      <c r="N83" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="inlineStr">
-        <is>
-          <t>CopulaGANSynthesizer(1)</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C84" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D84" s="0" t="n">
-        <v>2005.126063</v>
-      </c>
-      <c r="E84" s="0" t="n">
-        <v>320.959614</v>
-      </c>
-      <c r="F84" s="0" t="n">
-        <v>3.796645</v>
-      </c>
-      <c r="G84" s="0" t="n">
-        <v>7.843599</v>
-      </c>
-      <c r="H84" s="0" t="n">
-        <v>11.339986</v>
-      </c>
-      <c r="I84" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="0" t="n">
-        <v>0.924008248697574</v>
-      </c>
-      <c r="K84" s="0" t="n">
-        <v>2013.058739</v>
-      </c>
-      <c r="L84" s="0" t="n">
-        <v>0.924008248697574</v>
-      </c>
-      <c r="M84" s="0" t="inlineStr"/>
-      <c r="N84" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="inlineStr">
-        <is>
-          <t>GaussianCopulaSynthesizer</t>
-        </is>
-      </c>
-      <c r="B85" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C85" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D85" s="0" t="n">
-        <v>42.389287</v>
-      </c>
-      <c r="E85" s="0" t="n">
-        <v>193.004936</v>
-      </c>
-      <c r="F85" s="0" t="n">
-        <v>0.780758</v>
-      </c>
-      <c r="G85" s="0" t="n">
-        <v>4.734066</v>
-      </c>
-      <c r="H85" s="0" t="n">
-        <v>10.4996</v>
-      </c>
-      <c r="I85" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="0" t="n">
-        <v>0.8689819291242673</v>
-      </c>
-      <c r="K85" s="0" t="n">
-        <v>47.225231</v>
-      </c>
-      <c r="L85" s="0" t="n">
-        <v>0.8689819291242673</v>
-      </c>
-      <c r="M85" s="0" t="inlineStr"/>
-      <c r="N85" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="inlineStr">
-        <is>
-          <t>RealTabFormerSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B86" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C86" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D86" s="0" t="inlineStr"/>
-      <c r="E86" s="0" t="inlineStr"/>
-      <c r="F86" s="0" t="inlineStr"/>
-      <c r="G86" s="0" t="inlineStr"/>
-      <c r="H86" s="0" t="inlineStr"/>
-      <c r="I86" s="0" t="inlineStr"/>
-      <c r="J86" s="0" t="inlineStr"/>
-      <c r="K86" s="0" t="n">
-        <v>0.137427</v>
-      </c>
-      <c r="L86" s="0" t="n">
-        <v>0.4340007147880677</v>
-      </c>
-      <c r="M86" s="0" t="inlineStr">
-        <is>
-          <t>RuntimeError: Error(s) in loading state_dict for GPT2LMHeadModel:
-	size mismatch for transformer.wte.weight: copying a param with shape torch.Size([386, 768]) from checkpoint, the shape in current model is torch.Size([891, 768]).</t>
-        </is>
-      </c>
-      <c r="N86" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="inlineStr">
-        <is>
-          <t>TVAESynthesizer</t>
-        </is>
-      </c>
-      <c r="B87" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C87" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D87" s="0" t="n">
-        <v>1425.108941</v>
-      </c>
-      <c r="E87" s="0" t="n">
-        <v>272.188011</v>
-      </c>
-      <c r="F87" s="0" t="n">
-        <v>2.687627</v>
-      </c>
-      <c r="G87" s="0" t="n">
-        <v>2.631622</v>
-      </c>
-      <c r="H87" s="0" t="n">
-        <v>9.657814</v>
-      </c>
-      <c r="I87" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="0" t="n">
-        <v>0.9332505991219198</v>
-      </c>
-      <c r="K87" s="0" t="n">
-        <v>1427.842441</v>
-      </c>
-      <c r="L87" s="0" t="n">
-        <v>0.9332505991219198</v>
-      </c>
-      <c r="M87" s="0" t="inlineStr"/>
-      <c r="N87" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer</t>
-        </is>
-      </c>
-      <c r="B88" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C88" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D88" s="0" t="n">
-        <v>0.259624</v>
-      </c>
-      <c r="E88" s="0" t="n">
-        <v>94.46044999999999</v>
-      </c>
-      <c r="F88" s="0" t="n">
-        <v>18.715492</v>
-      </c>
-      <c r="G88" s="0" t="n">
-        <v>0.078391</v>
-      </c>
-      <c r="H88" s="0" t="n">
-        <v>11.985718</v>
-      </c>
-      <c r="I88" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="0" t="n">
-        <v>0.7407564446665227</v>
-      </c>
-      <c r="K88" s="0" t="n">
-        <v>0.439893</v>
-      </c>
-      <c r="L88" s="0" t="n">
-        <v>0.7407564446665227</v>
-      </c>
-      <c r="M88" s="0" t="inlineStr"/>
-      <c r="N88" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(1)</t>
-        </is>
-      </c>
-      <c r="B89" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C89" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D89" s="0" t="n">
-        <v>0.25967</v>
-      </c>
-      <c r="E89" s="0" t="n">
-        <v>94.46084999999999</v>
-      </c>
-      <c r="F89" s="0" t="n">
-        <v>18.715492</v>
-      </c>
-      <c r="G89" s="0" t="n">
-        <v>0.077821</v>
-      </c>
-      <c r="H89" s="0" t="n">
-        <v>12.683264</v>
-      </c>
-      <c r="I89" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="0" t="n">
-        <v>0.7405637769330489</v>
-      </c>
-      <c r="K89" s="0" t="n">
-        <v>0.426568</v>
-      </c>
-      <c r="L89" s="0" t="n">
-        <v>0.7405637769330489</v>
-      </c>
-      <c r="M89" s="0" t="inlineStr"/>
-      <c r="N89" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(2)</t>
-        </is>
-      </c>
-      <c r="B90" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C90" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D90" s="0" t="n">
-        <v>0.258199</v>
-      </c>
-      <c r="E90" s="0" t="n">
-        <v>94.45906600000001</v>
-      </c>
-      <c r="F90" s="0" t="n">
-        <v>18.715492</v>
-      </c>
-      <c r="G90" s="0" t="n">
-        <v>0.077864</v>
-      </c>
-      <c r="H90" s="0" t="n">
-        <v>12.416015</v>
-      </c>
-      <c r="I90" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="0" t="n">
-        <v>0.740782562581715</v>
-      </c>
-      <c r="K90" s="0" t="n">
-        <v>0.427439</v>
-      </c>
-      <c r="L90" s="0" t="n">
-        <v>0.740782562581715</v>
-      </c>
-      <c r="M90" s="0" t="inlineStr"/>
-      <c r="N90" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="inlineStr">
-        <is>
-          <t>UniformSynthesizer(3)</t>
-        </is>
-      </c>
-      <c r="B91" s="0" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="C91" s="0" t="n">
-        <v>18.712096</v>
-      </c>
-      <c r="D91" s="0" t="n">
-        <v>0.252517</v>
-      </c>
-      <c r="E91" s="0" t="n">
-        <v>2791.557048</v>
-      </c>
-      <c r="F91" s="0" t="n">
-        <v>18.715492</v>
-      </c>
-      <c r="G91" s="0" t="n">
-        <v>0.084617</v>
-      </c>
-      <c r="H91" s="0" t="n">
-        <v>13.63422</v>
-      </c>
-      <c r="I91" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="0" t="n">
-        <v>0.7407251501202706</v>
-      </c>
-      <c r="K91" s="0" t="n">
-        <v>0.435456</v>
-      </c>
-      <c r="L91" s="0" t="n">
-        <v>0.7407251501202706</v>
-      </c>
-      <c r="M91" s="0" t="inlineStr"/>
-      <c r="N91" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -45423,7 +43995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45466,17 +44038,17 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>Uniform(2)</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>6.691829</v>
+        <v>6.861451</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.5519974633986426</v>
+        <v>0.5523385148727864</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.8255448346655427</v>
+        <v>0.8364159662399919</v>
       </c>
       <c r="E2" s="0" t="b">
         <v>1</v>
@@ -45495,17 +44067,17 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>Uniform(1)</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>6.861451</v>
+        <v>164.120893</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.5523385148727864</v>
+        <v>0.8029129828259545</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.8364159662399919</v>
+        <v>2.215163871345796</v>
       </c>
       <c r="E3" s="0" t="b">
         <v>1</v>
@@ -45524,17 +44096,17 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>6.900074</v>
+        <v>1216.030677</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.5525471376404104</v>
+        <v>0.8411841605426035</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.838853748363245</v>
+        <v>3.084944531091133</v>
       </c>
       <c r="E4" s="0" t="b">
         <v>1</v>
@@ -45553,17 +44125,17 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>Uniform(3)</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>7.144682</v>
+        <v>47931.735647</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.5525515734036687</v>
+        <v>0.9004582959979872</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.8539829037052051</v>
+        <v>4.680623155431741</v>
       </c>
       <c r="E5" s="0" t="b">
         <v>1</v>
@@ -45582,24 +44154,24 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>Column</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>164.120893</v>
+        <v>112269.63319</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.8029129828259545</v>
+        <v>0.8732605478341368</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>2.215163871345796</v>
+        <v>5.050262303710914</v>
       </c>
       <c r="E6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>#01E0C9</t>
+          <t>#03AFF1</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
@@ -45611,24 +44183,24 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>1216.030677</v>
+        <v>120453.58431</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.8411841605426035</v>
+        <v>0.825333285375822</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>3.084944531091133</v>
+        <v>5.080819727729081</v>
       </c>
       <c r="E7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>#01E0C9</t>
+          <t>#03AFF1</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
@@ -45640,116 +44212,29 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>RealTabFormer</t>
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>47931.735647</v>
+        <v>635086.814483</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.9004582959979872</v>
+        <v>0.6314866655746016</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>4.680623155431741</v>
+        <v>5.802833096116938</v>
       </c>
       <c r="E8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>#01E0C9</t>
+          <t>#03AFF1</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
           <t>triangle-down</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>CTGAN(2)</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>112269.63319</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0.8732605478341368</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>5.050262303710914</v>
-      </c>
-      <c r="E9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>#03AFF1</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>triangle-left</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>CopulaGAN(1)</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>120453.58431</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0.825333285375822</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>5.080819727729081</v>
-      </c>
-      <c r="E10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>#03AFF1</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>triangle-right</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>RealTabFormer(3)</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>635086.814483</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0.6314866655746016</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>5.802833096116938</v>
-      </c>
-      <c r="E11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>#03AFF1</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>pentagon</t>
         </is>
       </c>
     </row>
